--- a/output/pdf_financials_xlsx/TEMP.xlsx
+++ b/output/pdf_financials_xlsx/TEMP.xlsx
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.776017</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.56696</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.486965</v>
       </c>
     </row>
     <row r="11">
@@ -630,7 +630,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.0075</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -900,7 +900,7 @@
         <v>-1.867654</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.235282</v>
+        <v>-0.242782</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.458803</v>
@@ -932,7 +932,7 @@
         <v>-1.867654</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.235282</v>
+        <v>-0.242782</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.458803</v>
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.176818</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.026822</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.186502</v>
       </c>
     </row>
     <row r="35">
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.176818</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.026822</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.186502</v>
       </c>
     </row>
     <row r="37">
@@ -1236,13 +1236,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.188627</v>
+        <v>0.011809</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.235383</v>
+        <v>0.208561</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.345636</v>
+        <v>0.159134</v>
       </c>
     </row>
     <row r="49">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
@@ -5436,7 +5436,11 @@
           <t>Interest expense [14]</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -5562,7 +5566,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
@@ -5912,7 +5916,11 @@
           <t>Interest expense [15]</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E109" s="5" t="n">
         <v>0.375861</v>
       </c>
@@ -5976,7 +5984,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">

--- a/output/pdf_financials_xlsx/TEMP.xlsx
+++ b/output/pdf_financials_xlsx/TEMP.xlsx
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.01132</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -3909,7 +3909,11 @@
           <t>Deferred income taxes (recovery) [16]</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -4782,7 +4786,11 @@
           <t>Deferred income taxes (recovery) [17]</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
         <v>-0.300837</v>
       </c>
@@ -4933,7 +4941,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>0.01132</v>
       </c>
